--- a/tools/test/test-students.xlsx
+++ b/tools/test/test-students.xlsx
@@ -51,12 +51,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>course</t>
+          <t>branch</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>semester</t>
+          <t>batch</t>
         </is>
       </c>
     </row>
@@ -71,12 +71,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -92,7 +92,7 @@
       <c r="C3"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -103,7 +103,7 @@
       <c r="B4"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>MEC</t>
         </is>
       </c>
       <c r="D4"/>
